--- a/data/sankey/sankey_nodes-ste.xlsx
+++ b/data/sankey/sankey_nodes-ste.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\vapor\data\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00062D96-E5F2-4FF8-B8DC-CAF64BD8B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6641CBD-49CE-4C8E-9E10-D7BCD92E6898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -597,7 +597,7 @@
         <v>3.3</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I4:I14" si="1">PI()*(((G5-2*H5)*10^-3)^2)/4</f>
+        <f t="shared" ref="I5:I14" si="1">PI()*(((G5-2*H5)*10^-3)^2)/4</f>
         <v>1.4186929768786934E-2</v>
       </c>
       <c r="J5" s="3">

--- a/data/sankey/sankey_nodes-ste.xlsx
+++ b/data/sankey/sankey_nodes-ste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7079B909-7859-49AE-8473-906E3452589E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AEE704-E934-4D3A-AFE7-61C6A5D9FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>source</t>
   </si>
@@ -111,6 +111,45 @@
   </si>
   <si>
     <t>cabal kgh</t>
+  </si>
+  <si>
+    <t>extraccio</t>
+  </si>
+  <si>
+    <t>E-700</t>
+  </si>
+  <si>
+    <t>ext-nord</t>
+  </si>
+  <si>
+    <t>ext-sud</t>
+  </si>
+  <si>
+    <t>SS800</t>
+  </si>
+  <si>
+    <t>E900/E1000</t>
+  </si>
+  <si>
+    <t>SS-700B</t>
+  </si>
+  <si>
+    <t>SIL-PEL</t>
+  </si>
+  <si>
+    <t>dutxes</t>
+  </si>
+  <si>
+    <t>columnes</t>
+  </si>
+  <si>
+    <t>LIQ-LIQ</t>
+  </si>
+  <si>
+    <t>P600</t>
+  </si>
+  <si>
+    <t>A-201</t>
   </si>
 </sst>
 </file>
@@ -384,24 +423,21 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5">
-        <f>SUM(F7:F9)</f>
-        <v>1.7841175365571144E-2</v>
+        <v>1.7841175000000001E-2</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5">
-        <f>SUM(I7:I9)</f>
-        <v>418.23241601466566</v>
+        <v>521.02309519999994</v>
       </c>
       <c r="J2" s="5">
-        <f>I2*4.325</f>
-        <v>1808.8551992634291</v>
+        <v>2253.4248870000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
@@ -409,31 +445,31 @@
         <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>80</v>
+      </c>
       <c r="D3" s="5">
         <v>88.9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5">
+        <v>3.3</v>
+      </c>
       <c r="F3" s="5">
-        <f>PI()*(((D3-2*E3)*10^-3)^2)/4</f>
-        <v>6.2071666189443481E-3</v>
+        <v>5.3197299999999999E-3</v>
       </c>
       <c r="G3" s="6">
-        <v>4.5999999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="H3" s="5">
-        <f>G3*F3</f>
-        <v>2.8552966447143998E-2</v>
+        <v>3.9897970999999997E-2</v>
       </c>
       <c r="I3" s="5">
-        <f>H3*3600</f>
-        <v>102.79067920971839</v>
+        <v>143.6326972</v>
       </c>
       <c r="J3" s="5">
-        <f t="shared" ref="J3:J15" si="0">I3*4.325</f>
-        <v>444.56968758203203</v>
+        <v>621.21141539999996</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
@@ -441,35 +477,31 @@
         <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D4" s="5">
-        <v>88.9</v>
+        <v>141</v>
       </c>
       <c r="E4" s="5">
         <v>3.3</v>
       </c>
       <c r="F4" s="5">
-        <f>PI()*(((D4-2*E4)*10^-3)^2)/4</f>
-        <v>5.319729526158304E-3</v>
+        <v>1.418693E-2</v>
       </c>
       <c r="G4" s="6">
-        <v>7.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H4" s="5">
-        <f>G4*F4</f>
-        <v>3.9897971446187279E-2</v>
+        <v>3.2629937999999997E-2</v>
       </c>
       <c r="I4" s="5">
-        <f>H4*3600</f>
-        <v>143.6326972062742</v>
+        <v>117.46777849999999</v>
       </c>
       <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>621.21141541713598</v>
+        <v>508.04814199999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
@@ -477,137 +509,105 @@
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5">
-        <v>141</v>
-      </c>
-      <c r="E5" s="5">
-        <v>3.3</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E5" s="5"/>
       <c r="F5" s="5">
-        <f t="shared" ref="F5:F14" si="1">PI()*(((D5-2*E5)*10^-3)^2)/4</f>
-        <v>1.4186929768786934E-2</v>
+        <v>4.53646E-3</v>
       </c>
       <c r="G5" s="6">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H14" si="2">G5*F5</f>
-        <v>3.2629938468209947E-2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I14" si="3">H5*3600</f>
-        <v>117.46777848555581</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" si="0"/>
-        <v>508.04814195002888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>76</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
       <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>4.5364597917836608E-3</v>
+        <v>1.7841175000000001E-2</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="5">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>521.02309519999994</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2253.4248870000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5">
-        <v>50</v>
-      </c>
-      <c r="D7" s="5">
-        <v>60.3</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5">
-        <f t="shared" si="1"/>
-        <v>2.8557784079478277E-3</v>
-      </c>
-      <c r="G7" s="6">
-        <v>13.54</v>
-      </c>
-      <c r="H7" s="5">
-        <f t="shared" si="2"/>
-        <v>3.8667239643613585E-2</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="3"/>
-        <v>139.20206271700891</v>
-      </c>
-      <c r="J7" s="5">
-        <f t="shared" si="0"/>
-        <v>602.04892125106358</v>
-      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5">
-        <v>50</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="5">
-        <v>78</v>
+        <v>88.9</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.7783624261100756E-3</v>
+        <v>6.2071670000000004E-3</v>
       </c>
       <c r="G8" s="6">
-        <v>0.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="2"/>
-        <v>9.556724852220152E-4</v>
+        <v>2.8552965999999999E-2</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="3"/>
-        <v>3.4404209467992546</v>
+        <v>102.7906792</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="0"/>
-        <v>14.879820594906777</v>
+        <v>444.56968760000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
@@ -615,342 +615,473 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D9" s="5">
-        <v>114</v>
+        <v>60.3</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
-        <v>1.0207034531513238E-2</v>
+        <v>2.8557779999999998E-3</v>
       </c>
       <c r="G9" s="6">
-        <v>7.5</v>
+        <v>13.54</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="2"/>
-        <v>7.6552758986349292E-2</v>
+        <v>3.8667239999999999E-2</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="3"/>
-        <v>275.58993235085745</v>
+        <v>139.2020627</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
-        <v>1191.9264574174586</v>
+        <v>602.04892129999996</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>50</v>
+      </c>
+      <c r="D10" s="5">
+        <v>78</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5">
-        <f>SUM(F11:F12)</f>
-        <v>3.8397330810337844E-3</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="5"/>
+        <v>4.7783620000000004E-3</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>9.5567199999999997E-4</v>
+      </c>
       <c r="I10" s="5">
-        <f t="shared" ref="I10" si="4">SUM(I11:I12)</f>
-        <v>17.096836278775708</v>
+        <v>3.4404209469999998</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="0"/>
-        <v>73.943816905704935</v>
+        <v>14.87982059</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5">
-        <v>60.3</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2.7</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="E11" s="5"/>
       <c r="F11" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3671979184615426E-3</v>
+        <v>1.0207035E-2</v>
       </c>
       <c r="G11" s="6">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="H11" s="5">
-        <f t="shared" si="2"/>
-        <v>4.7343958369230853E-3</v>
+        <v>7.6552758999999998E-2</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="3"/>
-        <v>17.043825012923108</v>
+        <v>275.58993240000001</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="0"/>
-        <v>73.714543180892449</v>
+        <v>1191.926457</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="5">
-        <v>40</v>
-      </c>
-      <c r="D12" s="5">
-        <v>48.3</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" si="1"/>
-        <v>1.4725351625722418E-3</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="2"/>
-        <v>1.4725351625722417E-5</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="3"/>
-        <v>5.30112658526007E-2</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.22927372481249803</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>65</v>
-      </c>
-      <c r="D13" s="5">
-        <v>73</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5890811111671224E-3</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="2"/>
-        <v>3.5890811111671225E-4</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="3"/>
-        <v>1.2920692000201641</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="0"/>
-        <v>5.5881992900872097</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="5">
-        <v>65</v>
-      </c>
-      <c r="D14" s="5">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="E14" s="5">
-        <v>3.1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5">
-        <f t="shared" si="1"/>
-        <v>3.8704735651491607E-3</v>
-      </c>
-      <c r="G14" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="2"/>
-        <v>6.1927577042386571E-3</v>
-      </c>
+        <v>3.8397330000000001E-3</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="5">
-        <f t="shared" si="3"/>
-        <v>22.293927735259164</v>
+        <v>17.096836280000002</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="0"/>
-        <v>96.421237454995889</v>
+        <v>73.943816909999995</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="5">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2.367198E-3</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2</v>
+      </c>
+      <c r="H15" s="5">
+        <v>4.7343960000000001E-3</v>
+      </c>
+      <c r="I15" s="5">
+        <v>17.043825009999999</v>
+      </c>
+      <c r="J15" s="5">
+        <v>73.714543180000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5">
+        <v>40</v>
+      </c>
+      <c r="D16" s="5">
+        <v>48.3</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1.4725350000000001E-3</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1.47254E-5</v>
+      </c>
+      <c r="I16" s="5">
+        <v>5.3011266000000001E-2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0.22927372500000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>65</v>
+      </c>
+      <c r="D17" s="5">
+        <v>73</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3.589081E-3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3.5890800000000001E-4</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1.2920692</v>
+      </c>
+      <c r="J17" s="5">
+        <v>5.5881992900000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5">
+        <v>65</v>
+      </c>
+      <c r="D18" s="5">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="E18" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F18" s="5">
+        <v>3.870474E-3</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="H18" s="5">
+        <v>6.1927579999999996E-3</v>
+      </c>
+      <c r="I18" s="5">
+        <v>22.293927740000001</v>
+      </c>
+      <c r="J18" s="5">
+        <v>96.421237450000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5">
-        <f>SUM(F2:F6)</f>
-        <v>4.8091461071244387E-2</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <f>SUM(I2:I6)</f>
-        <v>782.12357091621402</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="0"/>
-        <v>3382.6844442126257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5">
+        <v>4.1884294000000002E-2</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5">
+        <v>782.1235709</v>
+      </c>
+      <c r="J19" s="5">
+        <v>3382.684444</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5">
+        <v>88.9</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5">
+        <v>6.2071670000000004E-3</v>
+      </c>
+      <c r="G20" s="5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2.8552965999999999E-2</v>
+      </c>
+      <c r="I20" s="5">
+        <v>102.7906792</v>
+      </c>
+      <c r="J20" s="5">
+        <v>444.56968760000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/data/sankey/sankey_nodes-ste.xlsx
+++ b/data/sankey/sankey_nodes-ste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AEE704-E934-4D3A-AFE7-61C6A5D9FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9607397B-6516-403E-8F9E-30170CDDCA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
   <si>
     <t>source</t>
   </si>
@@ -150,6 +150,21 @@
   </si>
   <si>
     <t>A-201</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>rgba(0,100,255,0.4)</t>
+  </si>
+  <si>
+    <t>rgba(0,255,0, 0.4)</t>
+  </si>
+  <si>
+    <t>rgba(0,0,0, 0.4)</t>
+  </si>
+  <si>
+    <t>rgba(255,0,255, 0.8)</t>
   </si>
 </sst>
 </file>
@@ -237,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,6 +260,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,156 +392,169 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="2" customWidth="1"/>
-    <col min="3" max="6" width="11.5546875" style="2"/>
-    <col min="7" max="7" width="14.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="11.5546875" style="2"/>
+    <col min="2" max="2" width="15.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19" style="2" customWidth="1"/>
+    <col min="4" max="7" width="11.5546875" style="2"/>
+    <col min="8" max="8" width="14.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5">
         <v>1.7841175000000001E-2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5">
+      <c r="H2" s="6"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
         <v>521.02309519999994</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>2253.4248870000001</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5">
         <v>80</v>
       </c>
-      <c r="D3" s="5">
+      <c r="E3" s="5">
         <v>88.9</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>3.3</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>5.3197299999999999E-3</v>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <v>7.5</v>
       </c>
-      <c r="H3" s="5">
+      <c r="I3" s="5">
         <v>3.9897970999999997E-2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="J3" s="5">
         <v>143.6326972</v>
       </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
         <v>621.21141539999996</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="5">
         <v>125</v>
       </c>
-      <c r="D4" s="5">
+      <c r="E4" s="5">
         <v>141</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>3.3</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G4" s="5">
         <v>1.418693E-2</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>3.2629937999999997E-2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>117.46777849999999</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>508.04814199999998</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="5">
         <v>65</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5" s="5">
         <v>76</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>4.53646E-3</v>
       </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>0</v>
       </c>
       <c r="I5" s="5">
@@ -533,16 +563,19 @@
       <c r="J5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5">
-        <v>0</v>
+      <c r="C6" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
@@ -551,1630 +584,1466 @@
         <v>0</v>
       </c>
       <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
         <v>1.7841175000000001E-2</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>521.02309519999994</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>2253.4248870000001</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
+      <c r="C8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5">
         <v>88.9</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
         <v>6.2071670000000004E-3</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>2.8552965999999999E-2</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>102.7906792</v>
       </c>
-      <c r="J8" s="5">
+      <c r="K8" s="5">
         <v>444.56968760000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="5">
         <v>50</v>
       </c>
-      <c r="D9" s="5">
+      <c r="E9" s="5">
         <v>60.3</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
         <v>2.8557779999999998E-3</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>13.54</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>3.8667239999999999E-2</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>139.2020627</v>
       </c>
-      <c r="J9" s="5">
+      <c r="K9" s="5">
         <v>602.04892129999996</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="5">
         <v>50</v>
       </c>
-      <c r="D10" s="5">
+      <c r="E10" s="5">
         <v>78</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
         <v>4.7783620000000004E-3</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>0.2</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>9.5567199999999997E-4</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>3.4404209469999998</v>
       </c>
-      <c r="J10" s="5">
+      <c r="K10" s="5">
         <v>14.87982059</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5">
         <v>100</v>
       </c>
-      <c r="D11" s="5">
+      <c r="E11" s="5">
         <v>114</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
         <v>1.0207035E-2</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>7.5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <v>7.6552758999999998E-2</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <v>275.58993240000001</v>
       </c>
-      <c r="J11" s="5">
+      <c r="K11" s="5">
         <v>1191.926457</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
         <v>3.8397330000000001E-3</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
+      <c r="H14" s="6"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
         <v>17.096836280000002</v>
       </c>
-      <c r="J14" s="5">
+      <c r="K14" s="5">
         <v>73.943816909999995</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="5">
         <v>50</v>
       </c>
-      <c r="D15" s="5">
+      <c r="E15" s="5">
         <v>60.3</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>2.7</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <v>2.367198E-3</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="6">
         <v>2</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>4.7343960000000001E-3</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>17.043825009999999</v>
       </c>
-      <c r="J15" s="5">
+      <c r="K15" s="5">
         <v>73.714543180000007</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="5">
         <v>40</v>
       </c>
-      <c r="D16" s="5">
+      <c r="E16" s="5">
         <v>48.3</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>2.5</v>
       </c>
-      <c r="F16" s="5">
+      <c r="G16" s="5">
         <v>1.4725350000000001E-3</v>
       </c>
-      <c r="G16" s="5">
+      <c r="H16" s="6">
         <v>0.01</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>1.47254E-5</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <v>5.3011266000000001E-2</v>
       </c>
-      <c r="J16" s="5">
+      <c r="K16" s="5">
         <v>0.22927372500000001</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="5">
         <v>65</v>
       </c>
-      <c r="D17" s="5">
+      <c r="E17" s="5">
         <v>73</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="5">
         <v>2.7</v>
       </c>
-      <c r="F17" s="5">
+      <c r="G17" s="5">
         <v>3.589081E-3</v>
       </c>
-      <c r="G17" s="5">
+      <c r="H17" s="6">
         <v>0.1</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>3.5890800000000001E-4</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>1.2920692</v>
       </c>
-      <c r="J17" s="5">
+      <c r="K17" s="5">
         <v>5.5881992900000004</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="5">
         <v>65</v>
       </c>
-      <c r="D18" s="5">
+      <c r="E18" s="5">
         <v>76.400000000000006</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>3.1</v>
       </c>
-      <c r="F18" s="5">
+      <c r="G18" s="5">
         <v>3.870474E-3</v>
       </c>
-      <c r="G18" s="5">
+      <c r="H18" s="6">
         <v>1.6</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <v>6.1927579999999996E-3</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <v>22.293927740000001</v>
       </c>
-      <c r="J18" s="5">
+      <c r="K18" s="5">
         <v>96.421237450000007</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="C19" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5">
         <v>4.1884294000000002E-2</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5">
+      <c r="H19" s="6"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
         <v>782.1235709</v>
       </c>
-      <c r="J19" s="5">
+      <c r="K19" s="5">
         <v>3382.684444</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5">
+      <c r="C20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5">
         <v>88.9</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5">
         <v>6.2071670000000004E-3</v>
       </c>
-      <c r="G20" s="5">
+      <c r="H20" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H20" s="5">
+      <c r="I20" s="5">
         <v>2.8552965999999999E-2</v>
       </c>
-      <c r="I20" s="5">
+      <c r="J20" s="5">
         <v>102.7906792</v>
       </c>
-      <c r="J20" s="5">
+      <c r="K20" s="5">
         <v>444.56968760000001</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="H21" s="6"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="6"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="5"/>
+      <c r="C23" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="H23" s="6"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="5"/>
+      <c r="C24" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="H24" s="6"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="6"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="H27" s="6"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="6"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-    </row>
-    <row r="54" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-    </row>
-    <row r="55" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-    </row>
-    <row r="61" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-    </row>
-    <row r="62" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-    </row>
-    <row r="64" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-    </row>
-    <row r="70" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-    </row>
-    <row r="71" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
-    </row>
-    <row r="72" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-    </row>
-    <row r="73" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-    </row>
-    <row r="74" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-    </row>
-    <row r="75" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-    </row>
-    <row r="76" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-    </row>
-    <row r="77" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-    </row>
-    <row r="78" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-    </row>
-    <row r="79" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-    </row>
-    <row r="80" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-    </row>
-    <row r="81" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-    </row>
-    <row r="82" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
-    </row>
-    <row r="83" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-    </row>
-    <row r="84" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-    </row>
-    <row r="85" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
-    </row>
-    <row r="86" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
-    </row>
-    <row r="87" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-    </row>
-    <row r="88" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-    </row>
-    <row r="89" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
-    </row>
-    <row r="90" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-    </row>
-    <row r="91" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-    </row>
-    <row r="92" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
-    </row>
-    <row r="93" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-    </row>
-    <row r="94" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-    </row>
-    <row r="95" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-    </row>
-    <row r="96" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
-    </row>
-    <row r="97" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
-    </row>
-    <row r="98" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-    </row>
-    <row r="101" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
-    </row>
-    <row r="102" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F101" s="1"/>
+    </row>
+    <row r="102" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
-    </row>
-    <row r="103" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
-    </row>
-    <row r="104" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-    </row>
-    <row r="105" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
-    </row>
-    <row r="106" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
-    </row>
-    <row r="107" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
-    </row>
-    <row r="108" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-    </row>
-    <row r="109" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
-    </row>
-    <row r="110" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
-    </row>
-    <row r="111" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-    </row>
-    <row r="112" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-    </row>
-    <row r="113" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-    </row>
-    <row r="114" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
-    </row>
-    <row r="115" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
-    </row>
-    <row r="116" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-    </row>
-    <row r="117" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
-    </row>
-    <row r="118" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
-    </row>
-    <row r="119" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
-    </row>
-    <row r="120" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-    </row>
-    <row r="121" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
-    </row>
-    <row r="122" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-    </row>
-    <row r="123" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
-    </row>
-    <row r="124" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-    </row>
-    <row r="125" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-    </row>
-    <row r="126" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F125" s="1"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
-    </row>
-    <row r="127" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F126" s="1"/>
+    </row>
+    <row r="127" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
-    </row>
-    <row r="128" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-    </row>
-    <row r="129" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F128" s="1"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
-    </row>
-    <row r="130" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F129" s="1"/>
+    </row>
+    <row r="130" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-    </row>
-    <row r="131" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F130" s="1"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
-    </row>
-    <row r="132" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F131" s="1"/>
+    </row>
+    <row r="132" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-    </row>
-    <row r="133" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F132" s="1"/>
+    </row>
+    <row r="133" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
-    </row>
-    <row r="134" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
-    </row>
-    <row r="135" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F134" s="1"/>
+    </row>
+    <row r="135" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
-    </row>
-    <row r="136" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
-    </row>
-    <row r="137" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F136" s="1"/>
+    </row>
+    <row r="137" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
     </row>
-    <row r="138" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
     </row>
-    <row r="139" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
-    </row>
-    <row r="140" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
-    </row>
-    <row r="141" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
-    </row>
-    <row r="142" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="E142" s="1"/>
-    </row>
-    <row r="143" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="E143" s="1"/>
-    </row>
-    <row r="144" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="E144" s="1"/>
-    </row>
-    <row r="145" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
-      <c r="E145" s="1"/>
-    </row>
-    <row r="146" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
-      <c r="E146" s="1"/>
-    </row>
-    <row r="147" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="1"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
-      <c r="E147" s="1"/>
-    </row>
-    <row r="148" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
-    </row>
-    <row r="149" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
-    </row>
-    <row r="150" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
-    </row>
-    <row r="151" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-      <c r="E151" s="1"/>
-    </row>
-    <row r="152" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
-      <c r="E152" s="1"/>
-    </row>
-    <row r="153" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
-    </row>
-    <row r="154" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-      <c r="E154" s="1"/>
-    </row>
-    <row r="155" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
-      <c r="E155" s="1"/>
-    </row>
-    <row r="156" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-      <c r="E156" s="1"/>
-    </row>
-    <row r="157" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
-      <c r="E157" s="1"/>
-    </row>
-    <row r="158" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
-      <c r="E158" s="1"/>
-    </row>
-    <row r="159" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-    </row>
-    <row r="160" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-    </row>
-    <row r="161" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
-      <c r="E161" s="1"/>
-    </row>
-    <row r="162" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
-      <c r="E162" s="1"/>
-    </row>
-    <row r="163" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
-      <c r="E163" s="1"/>
-    </row>
-    <row r="164" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="E164" s="1"/>
-    </row>
-    <row r="165" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="1"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="E165" s="1"/>
-    </row>
-    <row r="166" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="1"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-      <c r="E166" s="1"/>
-    </row>
-    <row r="167" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="1"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
-      <c r="E167" s="1"/>
-    </row>
-    <row r="168" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="1"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
-      <c r="E168" s="1"/>
-    </row>
-    <row r="169" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-    </row>
-    <row r="170" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="1"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
-      <c r="E170" s="1"/>
-    </row>
-    <row r="171" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="1"/>
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
-      <c r="E171" s="1"/>
-    </row>
-    <row r="172" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="1"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
-      <c r="E172" s="1"/>
-    </row>
-    <row r="173" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
-      <c r="E173" s="1"/>
-    </row>
-    <row r="174" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
-      <c r="E174" s="1"/>
-    </row>
-    <row r="175" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
-      <c r="E175" s="1"/>
-    </row>
-    <row r="176" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
-      <c r="E176" s="1"/>
-    </row>
-    <row r="177" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-    </row>
-    <row r="178" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-    </row>
-    <row r="179" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-    </row>
-    <row r="180" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
-    </row>
-    <row r="181" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
-    </row>
-    <row r="182" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
-    </row>
-    <row r="183" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="E183" s="1"/>
-    </row>
-    <row r="184" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
-      <c r="E184" s="1"/>
-    </row>
-    <row r="185" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
-    </row>
-    <row r="186" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-    </row>
-    <row r="187" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-    </row>
-    <row r="188" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/sankey/sankey_nodes-ste.xlsx
+++ b/data/sankey/sankey_nodes-ste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9607397B-6516-403E-8F9E-30170CDDCA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB4A65B-AA89-4CEF-8E03-75797E7EF4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
   <si>
     <t>source</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>rgba(255,0,255, 0.8)</t>
+  </si>
+  <si>
+    <t>rgba(0,255,0,0.4)</t>
   </si>
 </sst>
 </file>
@@ -522,7 +525,7 @@
         <v>1.418693E-2</v>
       </c>
       <c r="H4" s="6">
-        <v>2.2999999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="I4" s="5">
         <v>3.2629937999999997E-2</v>
@@ -555,7 +558,7 @@
         <v>4.53646E-3</v>
       </c>
       <c r="H5" s="6">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -759,7 +762,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -778,7 +781,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -987,7 +990,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">

--- a/data/sankey/sankey_nodes-ste.xlsx
+++ b/data/sankey/sankey_nodes-ste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB4A65B-AA89-4CEF-8E03-75797E7EF4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D478DA03-7B88-4507-BB59-A2F5C0CB84D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
   <si>
     <t>source</t>
   </si>
@@ -50,9 +50,6 @@
     <t>DN</t>
   </si>
   <si>
-    <t>E800</t>
-  </si>
-  <si>
     <t>secadores</t>
   </si>
   <si>
@@ -167,7 +164,13 @@
     <t>rgba(255,0,255, 0.8)</t>
   </si>
   <si>
-    <t>rgba(0,255,0,0.4)</t>
+    <t>rgba(0,100,255, 0.4)</t>
+  </si>
+  <si>
+    <t>rgba(255,255,0, 0.4)</t>
+  </si>
+  <si>
+    <t>E888</t>
   </si>
 </sst>
 </file>
@@ -415,42 +418,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -469,13 +472,13 @@
     </row>
     <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="5">
         <v>80</v>
@@ -504,13 +507,13 @@
     </row>
     <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5">
         <v>125</v>
@@ -539,13 +542,13 @@
     </row>
     <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D5" s="5">
         <v>65</v>
@@ -572,13 +575,13 @@
     </row>
     <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
@@ -607,13 +610,13 @@
     </row>
     <row r="7" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -626,13 +629,13 @@
     </row>
     <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
@@ -657,13 +660,13 @@
     </row>
     <row r="9" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="5">
         <v>50</v>
@@ -690,13 +693,13 @@
     </row>
     <row r="10" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="5">
         <v>50</v>
@@ -723,13 +726,13 @@
     </row>
     <row r="11" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5">
         <v>100</v>
@@ -756,13 +759,13 @@
     </row>
     <row r="12" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -775,13 +778,13 @@
     </row>
     <row r="13" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -794,13 +797,13 @@
     </row>
     <row r="14" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -819,13 +822,13 @@
     </row>
     <row r="15" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="5">
         <v>50</v>
@@ -854,13 +857,13 @@
     </row>
     <row r="16" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" s="5">
         <v>40</v>
@@ -889,13 +892,13 @@
     </row>
     <row r="17" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5">
         <v>65</v>
@@ -924,13 +927,13 @@
     </row>
     <row r="18" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5">
         <v>65</v>
@@ -959,13 +962,13 @@
     </row>
     <row r="19" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -984,13 +987,13 @@
     </row>
     <row r="20" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
@@ -1015,13 +1018,13 @@
     </row>
     <row r="21" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -1034,13 +1037,13 @@
     </row>
     <row r="22" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -1053,10 +1056,10 @@
     </row>
     <row r="23" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>40</v>
@@ -1072,10 +1075,10 @@
     </row>
     <row r="24" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>40</v>
@@ -1091,10 +1094,10 @@
     </row>
     <row r="25" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>40</v>
@@ -1110,10 +1113,10 @@
     </row>
     <row r="26" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>40</v>
@@ -1129,10 +1132,10 @@
     </row>
     <row r="27" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>40</v>
@@ -1148,13 +1151,13 @@
     </row>
     <row r="28" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
